--- a/backend/data/financials_by_company/1439.TW.xlsx
+++ b/backend/data/financials_by_company/1439.TW.xlsx
@@ -647,534 +647,534 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4888.721379</v>
       </c>
       <c r="C2" t="n">
-        <v>0.107068</v>
+        <v>0.071893</v>
       </c>
       <c r="D2" t="n">
-        <v>216037000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+        <v>215771000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>68000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>68000</v>
+      </c>
       <c r="G2" t="n">
-        <v>160500000</v>
+        <v>128274000</v>
       </c>
       <c r="H2" t="n">
-        <v>22243000</v>
+        <v>21709000</v>
       </c>
       <c r="I2" t="n">
-        <v>55821000</v>
+        <v>505266000</v>
       </c>
       <c r="J2" t="n">
-        <v>216037000</v>
+        <v>215839000</v>
       </c>
       <c r="K2" t="n">
-        <v>193794000</v>
+        <v>194130000</v>
       </c>
       <c r="L2" t="n">
-        <v>-6135000</v>
+        <v>-10029000</v>
       </c>
       <c r="M2" t="n">
-        <v>11742000</v>
+        <v>13709000</v>
       </c>
       <c r="N2" t="n">
-        <v>5607000</v>
+        <v>3680000</v>
       </c>
       <c r="O2" t="n">
-        <v>160500000</v>
+        <v>128210888.721379</v>
       </c>
       <c r="P2" t="n">
-        <v>160500000</v>
+        <v>128274000</v>
       </c>
       <c r="Q2" t="n">
-        <v>123897000</v>
+        <v>581834000</v>
       </c>
       <c r="R2" t="n">
-        <v>92035000</v>
+        <v>92029000</v>
       </c>
       <c r="S2" t="n">
         <v>92000000</v>
       </c>
       <c r="T2" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="U2" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="V2" t="n">
-        <v>160500000</v>
+        <v>128274000</v>
       </c>
       <c r="W2" t="n">
-        <v>160500000</v>
+        <v>128274000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>160500000</v>
+        <v>128274000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-2060000</v>
+        <v>-39176000</v>
       </c>
       <c r="AA2" t="n">
-        <v>162560000</v>
+        <v>167450000</v>
       </c>
       <c r="AB2" t="n">
-        <v>162560000</v>
+        <v>167450000</v>
       </c>
       <c r="AC2" t="n">
-        <v>19492000</v>
+        <v>12971000</v>
       </c>
       <c r="AD2" t="n">
-        <v>182052000</v>
+        <v>180421000</v>
       </c>
       <c r="AE2" t="n">
-        <v>16787000</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
+        <v>36424000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>68000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-68000</v>
+      </c>
       <c r="AH2" t="n">
-        <v>-6135000</v>
+        <v>-10029000</v>
       </c>
       <c r="AI2" t="n">
-        <v>11742000</v>
+        <v>13709000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5607000</v>
+        <v>3680000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-25769000</v>
+        <v>33701000</v>
       </c>
       <c r="AL2" t="n">
-        <v>68076000</v>
+        <v>76568000</v>
       </c>
       <c r="AM2" t="n">
-        <v>68076000</v>
+        <v>76568000</v>
       </c>
       <c r="AN2" t="n">
-        <v>3504000</v>
+        <v>29180000</v>
       </c>
       <c r="AO2" t="n">
-        <v>64572000</v>
+        <v>47388000</v>
       </c>
       <c r="AP2" t="n">
-        <v>42307000</v>
+        <v>110269000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>55821000</v>
+        <v>505266000</v>
       </c>
       <c r="AR2" t="n">
-        <v>98128000</v>
+        <v>615535000</v>
       </c>
       <c r="AS2" t="n">
-        <v>98128000</v>
+        <v>615535000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.020854</v>
+        <v>0.113827</v>
       </c>
       <c r="D3" t="n">
-        <v>234498000</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+        <v>195363000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
       <c r="G3" t="n">
-        <v>184402000</v>
+        <v>92205000</v>
       </c>
       <c r="H3" t="n">
-        <v>21736000</v>
+        <v>21663000</v>
       </c>
       <c r="I3" t="n">
-        <v>144009000</v>
+        <v>446013000</v>
       </c>
       <c r="J3" t="n">
-        <v>234498000</v>
+        <v>195363000</v>
       </c>
       <c r="K3" t="n">
-        <v>212762000</v>
+        <v>173700000</v>
       </c>
       <c r="L3" t="n">
-        <v>-7719000</v>
+        <v>-7926000</v>
       </c>
       <c r="M3" t="n">
-        <v>13467000</v>
+        <v>11664000</v>
       </c>
       <c r="N3" t="n">
-        <v>5748000</v>
+        <v>3738000</v>
       </c>
       <c r="O3" t="n">
-        <v>184402000</v>
+        <v>92205000</v>
       </c>
       <c r="P3" t="n">
-        <v>184402000</v>
+        <v>92205000</v>
       </c>
       <c r="Q3" t="n">
-        <v>212286000</v>
+        <v>529302000</v>
       </c>
       <c r="R3" t="n">
-        <v>92063000</v>
+        <v>92000000</v>
       </c>
       <c r="S3" t="n">
         <v>92000000</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1.14</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>1.14</v>
       </c>
       <c r="V3" t="n">
-        <v>184402000</v>
+        <v>92205000</v>
       </c>
       <c r="W3" t="n">
-        <v>184402000</v>
+        <v>92205000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>184402000</v>
+        <v>92205000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-10737000</v>
+        <v>-51387000</v>
       </c>
       <c r="AA3" t="n">
-        <v>195139000</v>
+        <v>143592000</v>
       </c>
       <c r="AB3" t="n">
-        <v>195139000</v>
+        <v>143592000</v>
       </c>
       <c r="AC3" t="n">
-        <v>4156000</v>
+        <v>18444000</v>
       </c>
       <c r="AD3" t="n">
-        <v>199295000</v>
+        <v>162036000</v>
       </c>
       <c r="AE3" t="n">
-        <v>6838000</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
+        <v>-37507000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
       <c r="AH3" t="n">
-        <v>-7719000</v>
+        <v>-7926000</v>
       </c>
       <c r="AI3" t="n">
-        <v>13467000</v>
+        <v>11664000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>5748000</v>
+        <v>3738000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-13095000</v>
+        <v>40851000</v>
       </c>
       <c r="AL3" t="n">
-        <v>68277000</v>
+        <v>83289000</v>
       </c>
       <c r="AM3" t="n">
-        <v>68277000</v>
+        <v>83289000</v>
       </c>
       <c r="AN3" t="n">
-        <v>11326000</v>
+        <v>32469000</v>
       </c>
       <c r="AO3" t="n">
-        <v>56951000</v>
+        <v>50820000</v>
       </c>
       <c r="AP3" t="n">
-        <v>55182000</v>
+        <v>124140000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>144009000</v>
+        <v>446013000</v>
       </c>
       <c r="AR3" t="n">
-        <v>199191000</v>
+        <v>570153000</v>
       </c>
       <c r="AS3" t="n">
-        <v>199191000</v>
+        <v>570153000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.113827</v>
+        <v>0.020854</v>
       </c>
       <c r="D4" t="n">
-        <v>195363000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+        <v>234498000</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>92205000</v>
+        <v>184402000</v>
       </c>
       <c r="H4" t="n">
-        <v>21663000</v>
+        <v>21736000</v>
       </c>
       <c r="I4" t="n">
-        <v>446013000</v>
+        <v>144009000</v>
       </c>
       <c r="J4" t="n">
-        <v>195363000</v>
+        <v>234498000</v>
       </c>
       <c r="K4" t="n">
-        <v>173700000</v>
+        <v>212762000</v>
       </c>
       <c r="L4" t="n">
-        <v>-7926000</v>
+        <v>-7719000</v>
       </c>
       <c r="M4" t="n">
-        <v>11664000</v>
+        <v>13467000</v>
       </c>
       <c r="N4" t="n">
-        <v>3738000</v>
+        <v>5748000</v>
       </c>
       <c r="O4" t="n">
-        <v>92205000</v>
+        <v>184402000</v>
       </c>
       <c r="P4" t="n">
-        <v>92205000</v>
+        <v>184402000</v>
       </c>
       <c r="Q4" t="n">
-        <v>529302000</v>
+        <v>212286000</v>
       </c>
       <c r="R4" t="n">
-        <v>92000000</v>
+        <v>92063000</v>
       </c>
       <c r="S4" t="n">
         <v>92000000</v>
       </c>
       <c r="T4" t="n">
-        <v>1.14</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.14</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>92205000</v>
+        <v>184402000</v>
       </c>
       <c r="W4" t="n">
-        <v>92205000</v>
+        <v>184402000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>92205000</v>
+        <v>184402000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-51387000</v>
+        <v>-10737000</v>
       </c>
       <c r="AA4" t="n">
-        <v>143592000</v>
+        <v>195139000</v>
       </c>
       <c r="AB4" t="n">
-        <v>143592000</v>
+        <v>195139000</v>
       </c>
       <c r="AC4" t="n">
-        <v>18444000</v>
+        <v>4156000</v>
       </c>
       <c r="AD4" t="n">
-        <v>162036000</v>
+        <v>199295000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-37507000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
+        <v>6838000</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>-7926000</v>
+        <v>-7719000</v>
       </c>
       <c r="AI4" t="n">
-        <v>11664000</v>
+        <v>13467000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3738000</v>
+        <v>5748000</v>
       </c>
       <c r="AK4" t="n">
-        <v>40851000</v>
+        <v>-13095000</v>
       </c>
       <c r="AL4" t="n">
-        <v>83289000</v>
+        <v>68277000</v>
       </c>
       <c r="AM4" t="n">
-        <v>83289000</v>
+        <v>68277000</v>
       </c>
       <c r="AN4" t="n">
-        <v>32469000</v>
+        <v>11326000</v>
       </c>
       <c r="AO4" t="n">
-        <v>50820000</v>
+        <v>56951000</v>
       </c>
       <c r="AP4" t="n">
-        <v>124140000</v>
+        <v>55182000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>446013000</v>
+        <v>144009000</v>
       </c>
       <c r="AR4" t="n">
-        <v>570153000</v>
+        <v>199191000</v>
       </c>
       <c r="AS4" t="n">
-        <v>570153000</v>
+        <v>199191000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>4888.721379</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.071893</v>
+        <v>0.107068</v>
       </c>
       <c r="D5" t="n">
-        <v>215771000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>68000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>68000</v>
-      </c>
+        <v>216037000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>128274000</v>
+        <v>160500000</v>
       </c>
       <c r="H5" t="n">
-        <v>21709000</v>
+        <v>22243000</v>
       </c>
       <c r="I5" t="n">
-        <v>505266000</v>
+        <v>55821000</v>
       </c>
       <c r="J5" t="n">
-        <v>215839000</v>
+        <v>216037000</v>
       </c>
       <c r="K5" t="n">
-        <v>194130000</v>
+        <v>193794000</v>
       </c>
       <c r="L5" t="n">
-        <v>-10029000</v>
+        <v>-6135000</v>
       </c>
       <c r="M5" t="n">
-        <v>13709000</v>
+        <v>11742000</v>
       </c>
       <c r="N5" t="n">
-        <v>3680000</v>
+        <v>5607000</v>
       </c>
       <c r="O5" t="n">
-        <v>128210888.721379</v>
+        <v>160500000</v>
       </c>
       <c r="P5" t="n">
-        <v>128274000</v>
+        <v>160500000</v>
       </c>
       <c r="Q5" t="n">
-        <v>581834000</v>
+        <v>123897000</v>
       </c>
       <c r="R5" t="n">
-        <v>92029000</v>
+        <v>92035000</v>
       </c>
       <c r="S5" t="n">
         <v>92000000</v>
       </c>
       <c r="T5" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="U5" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="V5" t="n">
-        <v>128274000</v>
+        <v>160500000</v>
       </c>
       <c r="W5" t="n">
-        <v>128274000</v>
+        <v>160500000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>128274000</v>
+        <v>160500000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-39176000</v>
+        <v>-2060000</v>
       </c>
       <c r="AA5" t="n">
-        <v>167450000</v>
+        <v>162560000</v>
       </c>
       <c r="AB5" t="n">
-        <v>167450000</v>
+        <v>162560000</v>
       </c>
       <c r="AC5" t="n">
-        <v>12971000</v>
+        <v>19492000</v>
       </c>
       <c r="AD5" t="n">
-        <v>180421000</v>
+        <v>182052000</v>
       </c>
       <c r="AE5" t="n">
-        <v>36424000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>68000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-68000</v>
-      </c>
+        <v>16787000</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>-10029000</v>
+        <v>-6135000</v>
       </c>
       <c r="AI5" t="n">
-        <v>13709000</v>
+        <v>11742000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3680000</v>
+        <v>5607000</v>
       </c>
       <c r="AK5" t="n">
-        <v>33701000</v>
+        <v>-25769000</v>
       </c>
       <c r="AL5" t="n">
-        <v>76568000</v>
+        <v>68076000</v>
       </c>
       <c r="AM5" t="n">
-        <v>76568000</v>
+        <v>68076000</v>
       </c>
       <c r="AN5" t="n">
-        <v>29180000</v>
+        <v>3504000</v>
       </c>
       <c r="AO5" t="n">
-        <v>47388000</v>
+        <v>64572000</v>
       </c>
       <c r="AP5" t="n">
-        <v>110269000</v>
+        <v>42307000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>505266000</v>
+        <v>55821000</v>
       </c>
       <c r="AR5" t="n">
-        <v>615535000</v>
+        <v>98128000</v>
       </c>
       <c r="AS5" t="n">
-        <v>615535000</v>
+        <v>98128000</v>
       </c>
     </row>
   </sheetData>
@@ -1495,7 +1495,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>92000000</v>
@@ -1504,47 +1504,49 @@
         <v>92000000</v>
       </c>
       <c r="D2" t="n">
-        <v>1403918000</v>
+        <v>282786000</v>
       </c>
       <c r="E2" t="n">
-        <v>2066038000</v>
+        <v>1359440000</v>
       </c>
       <c r="F2" t="n">
-        <v>2772009000</v>
+        <v>2614496000</v>
       </c>
       <c r="G2" t="n">
-        <v>4683157000</v>
+        <v>3851096000</v>
       </c>
       <c r="H2" t="n">
-        <v>1220904000</v>
+        <v>1281058000</v>
       </c>
       <c r="I2" t="n">
-        <v>2772009000</v>
+        <v>2614496000</v>
       </c>
       <c r="J2" t="n">
-        <v>157749000</v>
+        <v>122840000</v>
       </c>
       <c r="K2" t="n">
-        <v>2774868000</v>
+        <v>2614496000</v>
       </c>
       <c r="L2" t="n">
-        <v>3132868000</v>
+        <v>2614496000</v>
       </c>
       <c r="M2" t="n">
-        <v>3181039000</v>
+        <v>3320231000</v>
       </c>
       <c r="N2" t="n">
-        <v>406171000</v>
+        <v>705735000</v>
       </c>
       <c r="O2" t="n">
-        <v>2774868000</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>2614496000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>347601000</v>
+      </c>
       <c r="Q2" t="n">
-        <v>1251014000</v>
+        <v>969473000</v>
       </c>
       <c r="R2" t="n">
-        <v>227986000</v>
+        <v>145021000</v>
       </c>
       <c r="S2" t="n">
         <v>920000000</v>
@@ -1553,132 +1555,132 @@
         <v>920000000</v>
       </c>
       <c r="U2" t="n">
-        <v>2644044000</v>
+        <v>1556629000</v>
       </c>
       <c r="V2" t="n">
-        <v>517905000</v>
+        <v>127681000</v>
       </c>
       <c r="W2" t="n">
-        <v>8014000</v>
+        <v>7159000</v>
       </c>
       <c r="X2" t="n">
-        <v>30000</v>
+        <v>13000</v>
       </c>
       <c r="Y2" t="n">
-        <v>509861000</v>
+        <v>120509000</v>
       </c>
       <c r="Z2" t="n">
-        <v>151861000</v>
+        <v>120509000</v>
       </c>
       <c r="AA2" t="n">
-        <v>358000000</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2126139000</v>
+        <v>1428948000</v>
       </c>
       <c r="AC2" t="n">
-        <v>10676000</v>
+        <v>29786000</v>
       </c>
       <c r="AD2" t="n">
-        <v>1556177000</v>
+        <v>1238931000</v>
       </c>
       <c r="AE2" t="n">
-        <v>5888000</v>
+        <v>2331000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1550289000</v>
+        <v>1236600000</v>
       </c>
       <c r="AG2" t="n">
-        <v>165131000</v>
+        <v>100053000</v>
       </c>
       <c r="AH2" t="n">
-        <v>63040000</v>
+        <v>60797000</v>
       </c>
       <c r="AI2" t="n">
-        <v>17656000</v>
+        <v>5025000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>84435000</v>
+        <v>34231000</v>
       </c>
       <c r="AK2" t="n">
-        <v>5825083000</v>
+        <v>4876860000</v>
       </c>
       <c r="AL2" t="n">
-        <v>2478040000</v>
+        <v>2166854000</v>
       </c>
       <c r="AM2" t="n">
         <v>3790000</v>
       </c>
       <c r="AN2" t="n">
-        <v>10885000</v>
+        <v>10100000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1228000</v>
+        <v>2630000</v>
       </c>
       <c r="AP2" t="n">
-        <v>372737000</v>
+        <v>282568000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>154737000</v>
+        <v>196568000</v>
       </c>
       <c r="AR2" t="n">
-        <v>218000000</v>
+        <v>86000000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1299223000</v>
+        <v>965501000</v>
       </c>
       <c r="AT2" t="n">
-        <v>745599000</v>
+        <v>901576000</v>
       </c>
       <c r="AU2" t="n">
-        <v>2859000</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>41719000</v>
+        <v>689000</v>
       </c>
       <c r="AW2" t="n">
-        <v>41719000</v>
+        <v>689000</v>
       </c>
       <c r="AX2" t="n">
-        <v>41719000</v>
+        <v>689000</v>
       </c>
       <c r="AY2" t="n">
-        <v>3347043000</v>
+        <v>2710006000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>83005000</v>
+        <v>25936000</v>
       </c>
       <c r="BA2" t="n">
-        <v>8851000</v>
+        <v>2569000</v>
       </c>
       <c r="BB2" t="n">
-        <v>2487901000</v>
+        <v>1469857000</v>
       </c>
       <c r="BC2" t="n">
-        <v>52867000</v>
+        <v>226575000</v>
       </c>
       <c r="BD2" t="n">
-        <v>293000</v>
+        <v>109000</v>
       </c>
       <c r="BE2" t="n">
-        <v>2324000</v>
+        <v>11048000</v>
       </c>
       <c r="BF2" t="n">
-        <v>2324000</v>
+        <v>11048000</v>
       </c>
       <c r="BG2" t="n">
-        <v>711802000</v>
+        <v>973912000</v>
       </c>
       <c r="BH2" t="n">
-        <v>207431000</v>
+        <v>20098000</v>
       </c>
       <c r="BI2" t="n">
-        <v>504371000</v>
+        <v>953814000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>92000000</v>
@@ -1687,44 +1689,44 @@
         <v>92000000</v>
       </c>
       <c r="D3" t="n">
-        <v>1191490000</v>
+        <v>1243993000</v>
       </c>
       <c r="E3" t="n">
-        <v>1922253000</v>
+        <v>1892756000</v>
       </c>
       <c r="F3" t="n">
-        <v>2561779000</v>
+        <v>2272742000</v>
       </c>
       <c r="G3" t="n">
-        <v>4358372000</v>
+        <v>4038495000</v>
       </c>
       <c r="H3" t="n">
-        <v>1314945000</v>
+        <v>1256262000</v>
       </c>
       <c r="I3" t="n">
-        <v>2561779000</v>
+        <v>2272742000</v>
       </c>
       <c r="J3" t="n">
-        <v>125660000</v>
+        <v>127003000</v>
       </c>
       <c r="K3" t="n">
-        <v>2561779000</v>
+        <v>2272742000</v>
       </c>
       <c r="L3" t="n">
-        <v>2935779000</v>
+        <v>2662742000</v>
       </c>
       <c r="M3" t="n">
-        <v>3114778000</v>
+        <v>2815004000</v>
       </c>
       <c r="N3" t="n">
-        <v>552999000</v>
+        <v>542262000</v>
       </c>
       <c r="O3" t="n">
-        <v>2561779000</v>
+        <v>2272742000</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>955140000</v>
+        <v>1009210000</v>
       </c>
       <c r="R3" t="n">
         <v>182854000</v>
@@ -1736,132 +1738,130 @@
         <v>920000000</v>
       </c>
       <c r="U3" t="n">
-        <v>2192166000</v>
+        <v>2007760000</v>
       </c>
       <c r="V3" t="n">
-        <v>506168000</v>
+        <v>522155000</v>
       </c>
       <c r="W3" t="n">
-        <v>8697000</v>
+        <v>6942000</v>
       </c>
       <c r="X3" t="n">
-        <v>507000</v>
+        <v>511000</v>
       </c>
       <c r="Y3" t="n">
-        <v>496964000</v>
+        <v>514702000</v>
       </c>
       <c r="Z3" t="n">
-        <v>122964000</v>
+        <v>124702000</v>
       </c>
       <c r="AA3" t="n">
-        <v>374000000</v>
+        <v>390000000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1685998000</v>
+        <v>1485605000</v>
       </c>
       <c r="AC3" t="n">
-        <v>6096000</v>
+        <v>6958000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1425289000</v>
+        <v>1378054000</v>
       </c>
       <c r="AE3" t="n">
-        <v>2696000</v>
+        <v>2301000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1422593000</v>
+        <v>1375753000</v>
       </c>
       <c r="AG3" t="n">
-        <v>69295000</v>
+        <v>68895000</v>
       </c>
       <c r="AH3" t="n">
-        <v>37645000</v>
+        <v>29914000</v>
       </c>
       <c r="AI3" t="n">
-        <v>3553000</v>
+        <v>14180000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28097000</v>
+        <v>24801000</v>
       </c>
       <c r="AK3" t="n">
-        <v>5306944000</v>
+        <v>4822764000</v>
       </c>
       <c r="AL3" t="n">
-        <v>2306001000</v>
+        <v>2080897000</v>
       </c>
       <c r="AM3" t="n">
         <v>3790000</v>
       </c>
       <c r="AN3" t="n">
-        <v>10143000</v>
+        <v>10139000</v>
       </c>
       <c r="AO3" t="n">
-        <v>343000</v>
+        <v>338000</v>
       </c>
       <c r="AP3" t="n">
-        <v>269784000</v>
+        <v>239672000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>183784000</v>
+        <v>153672000</v>
       </c>
       <c r="AR3" t="n">
         <v>86000000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1155041000</v>
+        <v>939639000</v>
       </c>
       <c r="AT3" t="n">
-        <v>865808000</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
+        <v>887049000</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>1092000</v>
+        <v>270000</v>
       </c>
       <c r="AW3" t="n">
-        <v>1092000</v>
+        <v>270000</v>
       </c>
       <c r="AX3" t="n">
-        <v>1092000</v>
+        <v>270000</v>
       </c>
       <c r="AY3" t="n">
-        <v>3000943000</v>
+        <v>2741867000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>50347000</v>
+        <v>18475000</v>
       </c>
       <c r="BA3" t="n">
-        <v>7040000</v>
+        <v>3319000</v>
       </c>
       <c r="BB3" t="n">
-        <v>2172050000</v>
+        <v>2067819000</v>
       </c>
       <c r="BC3" t="n">
-        <v>37216000</v>
+        <v>43959000</v>
       </c>
       <c r="BD3" t="n">
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>7491000</v>
+        <v>6439000</v>
       </c>
       <c r="BF3" t="n">
-        <v>7491000</v>
+        <v>6439000</v>
       </c>
       <c r="BG3" t="n">
-        <v>726689000</v>
+        <v>601856000</v>
       </c>
       <c r="BH3" t="n">
-        <v>121586000</v>
+        <v>80096000</v>
       </c>
       <c r="BI3" t="n">
-        <v>605103000</v>
+        <v>521760000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>92000000</v>
@@ -1870,44 +1870,44 @@
         <v>92000000</v>
       </c>
       <c r="D4" t="n">
-        <v>1243993000</v>
+        <v>1191490000</v>
       </c>
       <c r="E4" t="n">
-        <v>1892756000</v>
+        <v>1922253000</v>
       </c>
       <c r="F4" t="n">
-        <v>2272742000</v>
+        <v>2561779000</v>
       </c>
       <c r="G4" t="n">
-        <v>4038495000</v>
+        <v>4358372000</v>
       </c>
       <c r="H4" t="n">
-        <v>1256262000</v>
+        <v>1314945000</v>
       </c>
       <c r="I4" t="n">
-        <v>2272742000</v>
+        <v>2561779000</v>
       </c>
       <c r="J4" t="n">
-        <v>127003000</v>
+        <v>125660000</v>
       </c>
       <c r="K4" t="n">
-        <v>2272742000</v>
+        <v>2561779000</v>
       </c>
       <c r="L4" t="n">
-        <v>2662742000</v>
+        <v>2935779000</v>
       </c>
       <c r="M4" t="n">
-        <v>2815004000</v>
+        <v>3114778000</v>
       </c>
       <c r="N4" t="n">
-        <v>542262000</v>
+        <v>552999000</v>
       </c>
       <c r="O4" t="n">
-        <v>2272742000</v>
+        <v>2561779000</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>1009210000</v>
+        <v>955140000</v>
       </c>
       <c r="R4" t="n">
         <v>182854000</v>
@@ -1919,130 +1919,132 @@
         <v>920000000</v>
       </c>
       <c r="U4" t="n">
-        <v>2007760000</v>
+        <v>2192166000</v>
       </c>
       <c r="V4" t="n">
-        <v>522155000</v>
+        <v>506168000</v>
       </c>
       <c r="W4" t="n">
-        <v>6942000</v>
+        <v>8697000</v>
       </c>
       <c r="X4" t="n">
-        <v>511000</v>
+        <v>507000</v>
       </c>
       <c r="Y4" t="n">
-        <v>514702000</v>
+        <v>496964000</v>
       </c>
       <c r="Z4" t="n">
-        <v>124702000</v>
+        <v>122964000</v>
       </c>
       <c r="AA4" t="n">
-        <v>390000000</v>
+        <v>374000000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1485605000</v>
+        <v>1685998000</v>
       </c>
       <c r="AC4" t="n">
-        <v>6958000</v>
+        <v>6096000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1378054000</v>
+        <v>1425289000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2301000</v>
+        <v>2696000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1375753000</v>
+        <v>1422593000</v>
       </c>
       <c r="AG4" t="n">
-        <v>68895000</v>
+        <v>69295000</v>
       </c>
       <c r="AH4" t="n">
-        <v>29914000</v>
+        <v>37645000</v>
       </c>
       <c r="AI4" t="n">
-        <v>14180000</v>
+        <v>3553000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24801000</v>
+        <v>28097000</v>
       </c>
       <c r="AK4" t="n">
-        <v>4822764000</v>
+        <v>5306944000</v>
       </c>
       <c r="AL4" t="n">
-        <v>2080897000</v>
+        <v>2306001000</v>
       </c>
       <c r="AM4" t="n">
         <v>3790000</v>
       </c>
       <c r="AN4" t="n">
-        <v>10139000</v>
+        <v>10143000</v>
       </c>
       <c r="AO4" t="n">
-        <v>338000</v>
+        <v>343000</v>
       </c>
       <c r="AP4" t="n">
-        <v>239672000</v>
+        <v>269784000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>153672000</v>
+        <v>183784000</v>
       </c>
       <c r="AR4" t="n">
         <v>86000000</v>
       </c>
       <c r="AS4" t="n">
-        <v>939639000</v>
+        <v>1155041000</v>
       </c>
       <c r="AT4" t="n">
-        <v>887049000</v>
-      </c>
-      <c r="AU4" t="inlineStr"/>
+        <v>865808000</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
       <c r="AV4" t="n">
-        <v>270000</v>
+        <v>1092000</v>
       </c>
       <c r="AW4" t="n">
-        <v>270000</v>
+        <v>1092000</v>
       </c>
       <c r="AX4" t="n">
-        <v>270000</v>
+        <v>1092000</v>
       </c>
       <c r="AY4" t="n">
-        <v>2741867000</v>
+        <v>3000943000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18475000</v>
+        <v>50347000</v>
       </c>
       <c r="BA4" t="n">
-        <v>3319000</v>
+        <v>7040000</v>
       </c>
       <c r="BB4" t="n">
-        <v>2067819000</v>
+        <v>2172050000</v>
       </c>
       <c r="BC4" t="n">
-        <v>43959000</v>
+        <v>37216000</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="BE4" t="n">
-        <v>6439000</v>
+        <v>7491000</v>
       </c>
       <c r="BF4" t="n">
-        <v>6439000</v>
+        <v>7491000</v>
       </c>
       <c r="BG4" t="n">
-        <v>601856000</v>
+        <v>726689000</v>
       </c>
       <c r="BH4" t="n">
-        <v>80096000</v>
+        <v>121586000</v>
       </c>
       <c r="BI4" t="n">
-        <v>521760000</v>
+        <v>605103000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>92000000</v>
@@ -2051,49 +2053,47 @@
         <v>92000000</v>
       </c>
       <c r="D5" t="n">
-        <v>282786000</v>
+        <v>1403918000</v>
       </c>
       <c r="E5" t="n">
-        <v>1359440000</v>
+        <v>2066038000</v>
       </c>
       <c r="F5" t="n">
-        <v>2614496000</v>
+        <v>2772009000</v>
       </c>
       <c r="G5" t="n">
-        <v>3851096000</v>
+        <v>4683157000</v>
       </c>
       <c r="H5" t="n">
-        <v>1281058000</v>
+        <v>1220904000</v>
       </c>
       <c r="I5" t="n">
-        <v>2614496000</v>
+        <v>2772009000</v>
       </c>
       <c r="J5" t="n">
-        <v>122840000</v>
+        <v>157749000</v>
       </c>
       <c r="K5" t="n">
-        <v>2614496000</v>
+        <v>2774868000</v>
       </c>
       <c r="L5" t="n">
-        <v>2614496000</v>
+        <v>3132868000</v>
       </c>
       <c r="M5" t="n">
-        <v>3320231000</v>
+        <v>3181039000</v>
       </c>
       <c r="N5" t="n">
-        <v>705735000</v>
+        <v>406171000</v>
       </c>
       <c r="O5" t="n">
-        <v>2614496000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>347601000</v>
-      </c>
+        <v>2774868000</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>969473000</v>
+        <v>1251014000</v>
       </c>
       <c r="R5" t="n">
-        <v>145021000</v>
+        <v>227986000</v>
       </c>
       <c r="S5" t="n">
         <v>920000000</v>
@@ -2102,127 +2102,127 @@
         <v>920000000</v>
       </c>
       <c r="U5" t="n">
-        <v>1556629000</v>
+        <v>2644044000</v>
       </c>
       <c r="V5" t="n">
-        <v>127681000</v>
+        <v>517905000</v>
       </c>
       <c r="W5" t="n">
-        <v>7159000</v>
+        <v>8014000</v>
       </c>
       <c r="X5" t="n">
-        <v>13000</v>
+        <v>30000</v>
       </c>
       <c r="Y5" t="n">
-        <v>120509000</v>
+        <v>509861000</v>
       </c>
       <c r="Z5" t="n">
-        <v>120509000</v>
+        <v>151861000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>358000000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1428948000</v>
+        <v>2126139000</v>
       </c>
       <c r="AC5" t="n">
-        <v>29786000</v>
+        <v>10676000</v>
       </c>
       <c r="AD5" t="n">
-        <v>1238931000</v>
+        <v>1556177000</v>
       </c>
       <c r="AE5" t="n">
-        <v>2331000</v>
+        <v>5888000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1236600000</v>
+        <v>1550289000</v>
       </c>
       <c r="AG5" t="n">
-        <v>100053000</v>
+        <v>165131000</v>
       </c>
       <c r="AH5" t="n">
-        <v>60797000</v>
+        <v>63040000</v>
       </c>
       <c r="AI5" t="n">
-        <v>5025000</v>
+        <v>17656000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34231000</v>
+        <v>84435000</v>
       </c>
       <c r="AK5" t="n">
-        <v>4876860000</v>
+        <v>5825083000</v>
       </c>
       <c r="AL5" t="n">
-        <v>2166854000</v>
+        <v>2478040000</v>
       </c>
       <c r="AM5" t="n">
         <v>3790000</v>
       </c>
       <c r="AN5" t="n">
-        <v>10100000</v>
+        <v>10885000</v>
       </c>
       <c r="AO5" t="n">
-        <v>2630000</v>
+        <v>1228000</v>
       </c>
       <c r="AP5" t="n">
-        <v>282568000</v>
+        <v>372737000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>196568000</v>
+        <v>154737000</v>
       </c>
       <c r="AR5" t="n">
-        <v>86000000</v>
+        <v>218000000</v>
       </c>
       <c r="AS5" t="n">
-        <v>965501000</v>
+        <v>1299223000</v>
       </c>
       <c r="AT5" t="n">
-        <v>901576000</v>
+        <v>745599000</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2859000</v>
       </c>
       <c r="AV5" t="n">
-        <v>689000</v>
+        <v>41719000</v>
       </c>
       <c r="AW5" t="n">
-        <v>689000</v>
+        <v>41719000</v>
       </c>
       <c r="AX5" t="n">
-        <v>689000</v>
+        <v>41719000</v>
       </c>
       <c r="AY5" t="n">
-        <v>2710006000</v>
+        <v>3347043000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>25936000</v>
+        <v>83005000</v>
       </c>
       <c r="BA5" t="n">
-        <v>2569000</v>
+        <v>8851000</v>
       </c>
       <c r="BB5" t="n">
-        <v>1469857000</v>
+        <v>2487901000</v>
       </c>
       <c r="BC5" t="n">
-        <v>226575000</v>
+        <v>52867000</v>
       </c>
       <c r="BD5" t="n">
-        <v>109000</v>
+        <v>293000</v>
       </c>
       <c r="BE5" t="n">
-        <v>11048000</v>
+        <v>2324000</v>
       </c>
       <c r="BF5" t="n">
-        <v>11048000</v>
+        <v>2324000</v>
       </c>
       <c r="BG5" t="n">
-        <v>973912000</v>
+        <v>711802000</v>
       </c>
       <c r="BH5" t="n">
-        <v>20098000</v>
+        <v>207431000</v>
       </c>
       <c r="BI5" t="n">
-        <v>953814000</v>
+        <v>504371000</v>
       </c>
     </row>
   </sheetData>
@@ -2528,52 +2528,56 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-312375000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>-202046000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
       <c r="D2" t="n">
-        <v>-175710000</v>
+        <v>-281902000</v>
       </c>
       <c r="E2" t="n">
-        <v>272286000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-7817000</v>
-      </c>
+        <v>393282000</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>504371000</v>
+        <v>953814000</v>
       </c>
       <c r="H2" t="n">
-        <v>605103000</v>
+        <v>1234310000</v>
       </c>
       <c r="I2" t="n">
-        <v>-100732000</v>
+        <v>-280496000</v>
       </c>
       <c r="J2" t="n">
-        <v>65201000</v>
+        <v>-32982000</v>
       </c>
       <c r="K2" t="n">
-        <v>-683000</v>
+        <v>82000</v>
       </c>
       <c r="L2" t="n">
-        <v>-27600000</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+        <v>-143057000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
       <c r="O2" t="n">
-        <v>96576000</v>
+        <v>111380000</v>
       </c>
       <c r="P2" t="n">
-        <v>112576000</v>
+        <v>127380000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-159710000</v>
+        <v>-265902000</v>
       </c>
       <c r="R2" t="n">
-        <v>272286000</v>
+        <v>393282000</v>
       </c>
       <c r="S2" t="n">
         <v>-16000000</v>
@@ -2581,473 +2585,477 @@
       <c r="T2" t="n">
         <v>-16000000</v>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
       <c r="V2" t="n">
-        <v>138625000</v>
+        <v>-45468000</v>
       </c>
       <c r="W2" t="n">
-        <v>-742000</v>
+        <v>-79991000</v>
       </c>
       <c r="X2" t="n">
-        <v>5910000</v>
+        <v>3571000</v>
       </c>
       <c r="Y2" t="n">
-        <v>111533000</v>
+        <v>42424000</v>
       </c>
       <c r="Z2" t="n">
-        <v>58808000</v>
+        <v>-9690000</v>
       </c>
       <c r="AA2" t="n">
-        <v>124206000</v>
+        <v>439900000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-65398000</v>
+        <v>-449590000</v>
       </c>
       <c r="AC2" t="n">
-        <v>103233000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>103233000</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
       <c r="AF2" t="n">
-        <v>-132300000</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+        <v>-1782000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-1782000</v>
+      </c>
       <c r="AH2" t="n">
-        <v>-132300000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-2986000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-2986000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
-        <v>-4831000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
       <c r="AM2" t="n">
-        <v>-4831000</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-304558000</v>
+        <v>-202046000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-6934000</v>
+        <v>-16558000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-10427000</v>
+        <v>-13779000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-290110000</v>
+        <v>-219146000</v>
       </c>
       <c r="AR2" t="n">
-        <v>19700000</v>
+        <v>-5851000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-61387000</v>
+        <v>12896000</v>
       </c>
       <c r="AT2" t="n">
-        <v>80418000</v>
+        <v>-61012000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-2176000</v>
+        <v>26901000</v>
       </c>
       <c r="AV2" t="n">
-        <v>-315851000</v>
+        <v>-215124000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-10814000</v>
+        <v>23044000</v>
       </c>
       <c r="AX2" t="n">
-        <v>6135000</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+        <v>10029000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-68000</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>22243000</v>
+        <v>21709000</v>
       </c>
       <c r="BA2" t="n">
-        <v>492000</v>
+        <v>6000</v>
       </c>
       <c r="BB2" t="n">
-        <v>21751000</v>
+        <v>21703000</v>
       </c>
       <c r="BC2" t="n">
-        <v>-10348000</v>
-      </c>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
+        <v>-44397000</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
       <c r="BF2" t="n">
-        <v>182052000</v>
+        <v>180421000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-55887000</v>
+        <v>-619155000</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-301000000</v>
       </c>
       <c r="D3" t="n">
-        <v>-490882000</v>
+        <v>-543096000</v>
       </c>
       <c r="E3" t="n">
-        <v>489996000</v>
+        <v>1061557000</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>605103000</v>
+        <v>521760000</v>
       </c>
       <c r="H3" t="n">
-        <v>521760000</v>
+        <v>953814000</v>
       </c>
       <c r="I3" t="n">
-        <v>83343000</v>
+        <v>-432054000</v>
       </c>
       <c r="J3" t="n">
-        <v>-29358000</v>
+        <v>-33775000</v>
       </c>
       <c r="K3" t="n">
-        <v>1755000</v>
+        <v>-231217000</v>
       </c>
       <c r="L3" t="n">
-        <v>-27600000</v>
+        <v>-18400000</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-301000000</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-301000000</v>
       </c>
       <c r="O3" t="n">
-        <v>-886000</v>
+        <v>518461000</v>
       </c>
       <c r="P3" t="n">
-        <v>15114000</v>
+        <v>530461000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-474882000</v>
+        <v>-113096000</v>
       </c>
       <c r="R3" t="n">
-        <v>489996000</v>
+        <v>643557000</v>
       </c>
       <c r="S3" t="n">
-        <v>-16000000</v>
+        <v>-12000000</v>
       </c>
       <c r="T3" t="n">
-        <v>-16000000</v>
+        <v>-430000000</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>418000000</v>
       </c>
       <c r="V3" t="n">
-        <v>168588000</v>
+        <v>220876000</v>
       </c>
       <c r="W3" t="n">
-        <v>-4000</v>
+        <v>179961000</v>
       </c>
       <c r="X3" t="n">
-        <v>5294000</v>
+        <v>6999000</v>
       </c>
       <c r="Y3" t="n">
-        <v>92329000</v>
+        <v>92385000</v>
       </c>
       <c r="Z3" t="n">
-        <v>70969000</v>
+        <v>-58469000</v>
       </c>
       <c r="AA3" t="n">
-        <v>120446000</v>
+        <v>67411000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-49477000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
+        <v>-125880000</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>-55887000</v>
+        <v>-619155000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-14902000</v>
+        <v>-6390000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-13296000</v>
+        <v>-11709000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-41322000</v>
+        <v>-669112000</v>
       </c>
       <c r="AR3" t="n">
-        <v>30864000</v>
+        <v>-12136000</v>
       </c>
       <c r="AS3" t="n">
-        <v>18723000</v>
+        <v>-21017000</v>
       </c>
       <c r="AT3" t="n">
-        <v>10823000</v>
+        <v>-41203000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-3721000</v>
+        <v>-750000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-104231000</v>
+        <v>-597962000</v>
       </c>
       <c r="AW3" t="n">
-        <v>6220000</v>
+        <v>3956000</v>
       </c>
       <c r="AX3" t="n">
-        <v>7719000</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+        <v>7926000</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ3" t="n">
-        <v>21736000</v>
+        <v>21663000</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>21736000</v>
+        <v>21663000</v>
       </c>
       <c r="BC3" t="n">
-        <v>-1846000</v>
+        <v>-3354000</v>
       </c>
       <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
-        <v>199295000</v>
+        <v>162036000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-619155000</v>
+        <v>-55887000</v>
       </c>
       <c r="C4" t="n">
-        <v>-301000000</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-543096000</v>
+        <v>-490882000</v>
       </c>
       <c r="E4" t="n">
-        <v>1061557000</v>
+        <v>489996000</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
+        <v>605103000</v>
+      </c>
+      <c r="H4" t="n">
         <v>521760000</v>
       </c>
-      <c r="H4" t="n">
-        <v>953814000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-432054000</v>
+        <v>83343000</v>
       </c>
       <c r="J4" t="n">
-        <v>-33775000</v>
+        <v>-29358000</v>
       </c>
       <c r="K4" t="n">
-        <v>-231217000</v>
+        <v>1755000</v>
       </c>
       <c r="L4" t="n">
-        <v>-18400000</v>
+        <v>-27600000</v>
       </c>
       <c r="M4" t="n">
-        <v>-301000000</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-301000000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>518461000</v>
+        <v>-886000</v>
       </c>
       <c r="P4" t="n">
-        <v>530461000</v>
+        <v>15114000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-113096000</v>
+        <v>-474882000</v>
       </c>
       <c r="R4" t="n">
-        <v>643557000</v>
+        <v>489996000</v>
       </c>
       <c r="S4" t="n">
-        <v>-12000000</v>
+        <v>-16000000</v>
       </c>
       <c r="T4" t="n">
-        <v>-430000000</v>
+        <v>-16000000</v>
       </c>
       <c r="U4" t="n">
-        <v>418000000</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>220876000</v>
+        <v>168588000</v>
       </c>
       <c r="W4" t="n">
-        <v>179961000</v>
+        <v>-4000</v>
       </c>
       <c r="X4" t="n">
-        <v>6999000</v>
+        <v>5294000</v>
       </c>
       <c r="Y4" t="n">
-        <v>92385000</v>
+        <v>92329000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-58469000</v>
+        <v>70969000</v>
       </c>
       <c r="AA4" t="n">
-        <v>67411000</v>
+        <v>120446000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-125880000</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+        <v>-49477000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
         <v>0</v>
       </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
       <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
       <c r="AN4" t="n">
-        <v>-619155000</v>
+        <v>-55887000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-6390000</v>
+        <v>-14902000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-11709000</v>
+        <v>-13296000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-669112000</v>
+        <v>-41322000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-12136000</v>
+        <v>30864000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-21017000</v>
+        <v>18723000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-41203000</v>
+        <v>10823000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-750000</v>
+        <v>-3721000</v>
       </c>
       <c r="AV4" t="n">
-        <v>-597962000</v>
+        <v>-104231000</v>
       </c>
       <c r="AW4" t="n">
-        <v>3956000</v>
+        <v>6220000</v>
       </c>
       <c r="AX4" t="n">
-        <v>7926000</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
+        <v>7719000</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>21663000</v>
+        <v>21736000</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>21663000</v>
+        <v>21736000</v>
       </c>
       <c r="BC4" t="n">
-        <v>-3354000</v>
+        <v>-1846000</v>
       </c>
       <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
-        <v>162036000</v>
+        <v>199295000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-202046000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
+        <v>-312375000</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>-281902000</v>
+        <v>-175710000</v>
       </c>
       <c r="E5" t="n">
-        <v>393282000</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>272286000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-7817000</v>
+      </c>
       <c r="G5" t="n">
-        <v>953814000</v>
+        <v>504371000</v>
       </c>
       <c r="H5" t="n">
-        <v>1234310000</v>
+        <v>605103000</v>
       </c>
       <c r="I5" t="n">
-        <v>-280496000</v>
+        <v>-100732000</v>
       </c>
       <c r="J5" t="n">
-        <v>-32982000</v>
+        <v>65201000</v>
       </c>
       <c r="K5" t="n">
-        <v>82000</v>
+        <v>-683000</v>
       </c>
       <c r="L5" t="n">
-        <v>-143057000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
+        <v>-27600000</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>111380000</v>
+        <v>96576000</v>
       </c>
       <c r="P5" t="n">
-        <v>127380000</v>
+        <v>112576000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-265902000</v>
+        <v>-159710000</v>
       </c>
       <c r="R5" t="n">
-        <v>393282000</v>
+        <v>272286000</v>
       </c>
       <c r="S5" t="n">
         <v>-16000000</v>
@@ -3055,113 +3063,105 @@
       <c r="T5" t="n">
         <v>-16000000</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-45468000</v>
+        <v>138625000</v>
       </c>
       <c r="W5" t="n">
-        <v>-79991000</v>
+        <v>-742000</v>
       </c>
       <c r="X5" t="n">
-        <v>3571000</v>
+        <v>5910000</v>
       </c>
       <c r="Y5" t="n">
-        <v>42424000</v>
+        <v>111533000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-9690000</v>
+        <v>58808000</v>
       </c>
       <c r="AA5" t="n">
-        <v>439900000</v>
+        <v>124206000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-449590000</v>
+        <v>-65398000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
+        <v>103233000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>103233000</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>-1782000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-1782000</v>
-      </c>
+        <v>-132300000</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
+        <v>-132300000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-2986000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-2986000</v>
+      </c>
       <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
+        <v>-4831000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-4831000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-202046000</v>
+        <v>-304558000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-16558000</v>
+        <v>-6934000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-13779000</v>
+        <v>-10427000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-219146000</v>
+        <v>-290110000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-5851000</v>
+        <v>19700000</v>
       </c>
       <c r="AS5" t="n">
-        <v>12896000</v>
+        <v>-61387000</v>
       </c>
       <c r="AT5" t="n">
-        <v>-61012000</v>
+        <v>80418000</v>
       </c>
       <c r="AU5" t="n">
-        <v>26901000</v>
+        <v>-2176000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-215124000</v>
+        <v>-315851000</v>
       </c>
       <c r="AW5" t="n">
-        <v>23044000</v>
+        <v>-10814000</v>
       </c>
       <c r="AX5" t="n">
-        <v>10029000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>-68000</v>
-      </c>
+        <v>6135000</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>21709000</v>
+        <v>22243000</v>
       </c>
       <c r="BA5" t="n">
-        <v>6000</v>
+        <v>492000</v>
       </c>
       <c r="BB5" t="n">
-        <v>21703000</v>
+        <v>21751000</v>
       </c>
       <c r="BC5" t="n">
-        <v>-44397000</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
+        <v>-10348000</v>
+      </c>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
-        <v>180421000</v>
+        <v>182052000</v>
       </c>
     </row>
   </sheetData>
@@ -3721,182 +3721,182 @@
       </c>
       <c r="DE1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
         </is>
       </c>
       <c r="EO1" t="inlineStr">
@@ -4001,34 +4001,34 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>25.6</v>
+        <v>25.3</v>
       </c>
       <c r="V2" t="n">
-        <v>25.25</v>
+        <v>25</v>
       </c>
       <c r="W2" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="X2" t="n">
         <v>25</v>
       </c>
-      <c r="X2" t="n">
-        <v>25.75</v>
-      </c>
       <c r="Y2" t="n">
-        <v>25.6</v>
+        <v>25.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>25.25</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AB2" t="n">
         <v>25</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>25.75</v>
       </c>
       <c r="AC2" t="n">
         <v>0.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AE2" t="n">
         <v>1754265600</v>
@@ -4040,31 +4040,31 @@
         <v>3.05</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.134</v>
+        <v>0.113</v>
       </c>
       <c r="AI2" t="n">
-        <v>7.975078</v>
+        <v>7.570093</v>
       </c>
       <c r="AJ2" t="n">
-        <v>44831</v>
+        <v>41107</v>
       </c>
       <c r="AK2" t="n">
-        <v>44831</v>
+        <v>41107</v>
       </c>
       <c r="AL2" t="n">
-        <v>40641</v>
+        <v>38774</v>
       </c>
       <c r="AM2" t="n">
-        <v>81490</v>
+        <v>29702</v>
       </c>
       <c r="AN2" t="n">
-        <v>81490</v>
+        <v>29702</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>24.75</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -4073,13 +4073,13 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>2355200000</v>
+        <v>2235599872</v>
       </c>
       <c r="AT2" t="n">
-        <v>2355200000</v>
+        <v>2327600000</v>
       </c>
       <c r="AU2" t="n">
-        <v>24.6</v>
+        <v>24.2</v>
       </c>
       <c r="AV2" t="n">
         <v>32.15</v>
@@ -4091,19 +4091,19 @@
         <v>6.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.1293724</v>
+        <v>2.9704587</v>
       </c>
       <c r="AZ2" t="n">
-        <v>26.772</v>
+        <v>26.149</v>
       </c>
       <c r="BA2" t="n">
-        <v>28.28025</v>
+        <v>28.0175</v>
       </c>
       <c r="BB2" t="n">
         <v>0.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.01953125</v>
+        <v>0.019762846</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>3915333888</v>
+        <v>3795734016</v>
       </c>
       <c r="BG2" t="n">
         <v>0.3759</v>
@@ -4126,7 +4126,7 @@
         <v>92000000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.7559100399999999</v>
+        <v>0.75504994</v>
       </c>
       <c r="BK2" t="n">
         <v>0</v>
@@ -4138,7 +4138,7 @@
         <v>32.276</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.7931589999999999</v>
+        <v>0.75288135</v>
       </c>
       <c r="BO2" t="n">
         <v>1767139200</v>
@@ -4159,16 +4159,16 @@
         <v>3.21</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.202</v>
+        <v>5.043</v>
       </c>
       <c r="BV2" t="n">
-        <v>31.586</v>
+        <v>30.622</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0.18210864</v>
+        <v>-0.16086233</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BY2" t="n">
         <v>0.3</v>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="CB2" t="n">
-        <v>25.6</v>
+        <v>24.3</v>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
@@ -4284,141 +4284,141 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DE2" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DF2" t="n">
+        <v>1782106215</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>TAI</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>finmb_9870587</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>Asia/Taipei</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="DK2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>tw_market</t>
+        </is>
+      </c>
+      <c r="DM2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>Ascent Development Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
         <is>
           <t>ASCENT DEVELOPMENT CO LTD</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>Ascent Development Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>1780377298</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>TAI</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>finmb_9870587</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>Asia/Taipei</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="DN2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>tw_market</t>
-        </is>
-      </c>
       <c r="DP2" t="b">
         <v>0</v>
       </c>
       <c r="DQ2" t="n">
+        <v>946947600000</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>24.3 - 25.0</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>38774</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0.099998474</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.0041321684</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>24.2 - 32.15</t>
+        </is>
+      </c>
+      <c r="DY2" t="n">
+        <v>-7.8500023</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.24416803</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-16.086233</v>
+      </c>
+      <c r="EB2" t="n">
         <v>3.21</v>
       </c>
-      <c r="DR2" t="n">
-        <v>-1.171999</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-0.043777045</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-2.6802502</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.094774626</v>
-      </c>
-      <c r="DV2" t="n">
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>-1.8490009</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.0707102</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-3.7175007</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.13268496</v>
+      </c>
+      <c r="EH2" t="n">
         <v>20</v>
       </c>
-      <c r="DW2" t="n">
+      <c r="EI2" t="n">
         <v>20</v>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>Chuwa Wool Industry Co., (Taiwan) Ltd.</t>
         </is>
       </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="DZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>946947600000</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>25.0 - 25.75</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>40641</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>1</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>0.040650405</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>24.6 - 32.15</t>
-        </is>
-      </c>
-      <c r="EJ2" t="n">
-        <v>-6.550001</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>-0.20373254</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>-18.210865</v>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="EL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>-3.9525692</v>
       </c>
       <c r="EN2" t="n">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="EO2" t="inlineStr"/>
     </row>
